--- a/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 74,5</t>
+          <t>14,91; 73,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 9,91</t>
+          <t>-5,18; 9,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 3,51</t>
+          <t>-12,65; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 11,08</t>
+          <t>-6,83; 10,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 10,08</t>
+          <t>-11,14; 10,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 189,2</t>
+          <t>-43,89; 182,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 43,2</t>
+          <t>-69,17; 48,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 116,03</t>
+          <t>-40,36; 120,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 78,54</t>
+          <t>-47,59; 80,45</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 12,21</t>
+          <t>-4,9; 11,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 8,76</t>
+          <t>-7,09; 9,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 5,71</t>
+          <t>-7,89; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 12,94</t>
+          <t>-5,11; 13,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 106,62</t>
+          <t>-23,66; 92,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 54,76</t>
+          <t>-29,78; 66,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 47,41</t>
+          <t>-41,29; 41,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 95,77</t>
+          <t>-23,27; 113,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 12,16</t>
+          <t>-3,67; 12,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 12,84</t>
+          <t>-4,2; 12,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 4,99</t>
+          <t>-11,9; 5,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 6,23</t>
+          <t>-6,9; 5,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 64,48</t>
+          <t>-14,09; 67,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 68,75</t>
+          <t>-15,24; 70,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,03; 28,79</t>
+          <t>-42,0; 30,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 51,18</t>
+          <t>-37,56; 49,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,87</t>
+          <t>-1,19; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,02</t>
+          <t>-3,85; 6,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,43</t>
+          <t>-6,27; 3,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,07</t>
+          <t>-3,22; 6,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 51,36</t>
+          <t>-5,77; 55,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 36,2</t>
+          <t>-17,58; 36,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,16</t>
+          <t>-29,57; 19,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 43,57</t>
+          <t>-17,46; 46,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 73,68</t>
+          <t>14,03; 74,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 9,72</t>
+          <t>-4,92; 10,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 4,3</t>
+          <t>-13,08; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 10,99</t>
+          <t>-7,81; 11,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 10,34</t>
+          <t>-10,4; 10,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 182,38</t>
+          <t>-39,0; 177,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 48,23</t>
+          <t>-71,51; 49,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 120,21</t>
+          <t>-44,06; 117,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 80,45</t>
+          <t>-45,7; 88,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 11,59</t>
+          <t>-4,79; 11,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 9,83</t>
+          <t>-7,22; 10,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 5,42</t>
+          <t>-8,6; 5,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 13,83</t>
+          <t>-5,29; 13,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 92,58</t>
+          <t>-23,96; 91,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 66,03</t>
+          <t>-31,36; 64,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 41,93</t>
+          <t>-43,84; 44,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 113,37</t>
+          <t>-26,38; 103,91</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 12,21</t>
+          <t>-3,22; 12,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 12,61</t>
+          <t>-4,87; 11,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 5,37</t>
+          <t>-12,04; 4,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 5,77</t>
+          <t>-6,31; 5,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 67,19</t>
+          <t>-12,83; 66,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 70,15</t>
+          <t>-17,68; 57,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 30,34</t>
+          <t>-43,17; 24,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 49,09</t>
+          <t>-34,52; 48,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,08</t>
+          <t>-1,11; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,07</t>
+          <t>-3,58; 5,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,18</t>
+          <t>-5,9; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,53</t>
+          <t>-3,75; 6,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 55,01</t>
+          <t>-5,84; 53,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 36,25</t>
+          <t>-15,87; 33,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 19,71</t>
+          <t>-28,37; 19,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 46,99</t>
+          <t>-19,62; 43,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,77</t>
+          <t>37,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 74,76</t>
+          <t>12,03; 71,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,26%</t>
+          <t>-2,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 10,07</t>
+          <t>-5,32; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 4,02</t>
+          <t>-12,69; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 11,44</t>
+          <t>-8,16; 11,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 10,59</t>
+          <t>-11,68; 10,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 177,86</t>
+          <t>-43,47; 189,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,51; 49,32</t>
+          <t>-68,66; 43,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 117,51</t>
+          <t>-44,81; 116,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 88,09</t>
+          <t>-46,92; 74,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 11,41</t>
+          <t>-4,42; 12,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 10,02</t>
+          <t>-6,93; 8,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,62</t>
+          <t>-8,51; 5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 13,31</t>
+          <t>-5,83; 10,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 91,4</t>
+          <t>-24,4; 106,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 64,57</t>
+          <t>-30,67; 54,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 44,34</t>
+          <t>-43,5; 47,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 103,91</t>
+          <t>-29,01; 86,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,9%</t>
+          <t>-0,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 12,38</t>
+          <t>-3,13; 12,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 11,27</t>
+          <t>-4,17; 12,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 4,25</t>
+          <t>-10,99; 4,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 5,88</t>
+          <t>-6,43; 6,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 66,44</t>
+          <t>-12,29; 64,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 57,0</t>
+          <t>-15,97; 68,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 24,08</t>
+          <t>-41,03; 28,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 48,0</t>
+          <t>-34,66; 55,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,28</t>
+          <t>-1,56; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,76</t>
+          <t>-3,68; 6,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,11</t>
+          <t>-5,63; 3,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,28</t>
+          <t>-3,43; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 53,74</t>
+          <t>-8,24; 51,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 33,59</t>
+          <t>-16,24; 36,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 19,42</t>
+          <t>-26,95; 22,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 43,85</t>
+          <t>-19,66; 40,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>37.25483614967826</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +644,142 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12,03; 71,53</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>12.03114959172852</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>71.53131238550699</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,57</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>27,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 9,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,69; 3,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 11,08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,68; 10,08</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-43,47; 189,2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-68,66; 43,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-44,81; 116,03</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-46,92; 74,07</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.465282822710325</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.568697492626769</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.566370993935581</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4630181658763666</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2727069598443425</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3313528964902864</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1131884265292766</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.02368078530707037</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,01</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-8,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.323032887796201</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-12.68684422203921</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-8.16479765258191</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.68158384281568</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4346685860706326</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6865621919769512</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4480872602263914</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4691746588936997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 12,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,93; 8,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,51; 5,71</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,83; 10,39</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-24,4; 106,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-30,67; 54,76</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-43,5; 47,41</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-29,01; 86,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.910134852482255</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.509197631557846</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.07556426223783</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.07802524818867</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.892032704819546</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.431988948750227</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.160318233681751</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7406695988957896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +787,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-13,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,08%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.009041958119321</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.747720362195085</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.318624611307784</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.405028511306453</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1802151492358036</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.09031785659146858</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.08073573477638617</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.149916607032389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 12,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 12,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 4,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 6,6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-12,29; 64,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-15,97; 68,75</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-41,03; 28,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-34,66; 55,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.418817505261226</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.928613595629589</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.506730482429294</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.83157999503122</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2440199744452108</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.30668287164156</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4350038706856116</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2900542811009784</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>12.21225658555901</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.760860155779501</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.71053347417899</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.38908198623996</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.066194302316203</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5476315460155783</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.4741431851869699</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.8637181915377654</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4.436993398827513</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.535542050820201</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-3.199086788535705</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.01155963957026884</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1999288419788877</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1524911537500104</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1388588387231216</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.0007770196998241666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.129662667725888</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.16809517536462</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-10.99022364749548</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.430281906899632</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1228835744666667</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1597335125198773</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4103064166424506</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3466364290517292</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>12.16161405646337</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>12.84402399114728</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.988688921806448</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.598151746170402</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6448034342672874</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6874609597137701</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.287919424908565</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5574788277200883</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-6,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 7,87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 6,02</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 3,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 5,54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; 51,36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-16,24; 36,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-26,95; 22,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,66; 40,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.195259145257123</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.242244785383304</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.197430948146572</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.182347233879991</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1821031286744006</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.06402929473860157</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.06581632759428456</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07481427292244748</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.563120393880569</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.677277002867448</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.628604645530022</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.430634351798952</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.08241125215799043</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1624184683845573</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2694787922735372</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1966384700889748</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.866137563631765</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.019567994140757</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.433660951318086</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.537416335800693</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5135953675968137</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3620196931720713</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.221639448007089</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.4004741970520224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1085,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
